--- a/data/trans_dic/P1802_2016_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1802_2016_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,27</t>
+          <t>10,08; 15,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,88</t>
+          <t>11,27; 16,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,64</t>
+          <t>14,5; 20,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 19,43</t>
+          <t>14,56; 19,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 16,89</t>
+          <t>13,02; 17,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 17,67</t>
+          <t>13,58; 17,14</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,86; 18,57</t>
+          <t>13,92; 18,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 66,35</t>
+          <t>10,76; 15,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,17</t>
+          <t>17,86; 23,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 16,26</t>
+          <t>12,79; 16,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 20,28</t>
+          <t>16,56; 20,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 48,7</t>
+          <t>12,35; 15,23</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 16,57</t>
+          <t>11,43; 16,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 17,38</t>
+          <t>11,34; 16,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,98</t>
+          <t>16,39; 22,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 19,63</t>
+          <t>17,43; 22,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,7; 18,74</t>
+          <t>14,62; 18,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,52</t>
+          <t>14,97; 18,65</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,31</t>
+          <t>11,91; 16,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,72</t>
+          <t>17,44; 22,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 20,47</t>
+          <t>15,75; 20,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 24,62</t>
+          <t>20,92; 25,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 17,97</t>
+          <t>14,64; 18,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 23,4</t>
+          <t>20,02; 23,22</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,7</t>
+          <t>13,19; 15,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,49; 39,25</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 20,25</t>
+          <t>17,52; 20,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,84</t>
+          <t>17,7; 19,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 17,69</t>
+          <t>15,76; 17,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 29,79</t>
+          <t>16,12; 17,77</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>122864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>205205</t>
+          <t>217846</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68107; 103071</t>
+          <t>67995; 102711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73475; 107249</t>
+          <t>77856; 113444</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97977; 138879</t>
+          <t>97561; 136870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99860; 131279</t>
+          <t>106767; 140199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>176149; 227654</t>
+          <t>175521; 229715</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>181663; 231718</t>
+          <t>193367; 244039</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>372269</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137267</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>509536</t>
+          <t>292340</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>141680; 189839</t>
+          <t>142322; 190696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>150778; 791436</t>
+          <t>112862; 158217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191876; 241601</t>
+          <t>186226; 240622</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121117; 155782</t>
+          <t>136936; 177771</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>345259; 418933</t>
+          <t>342061; 417940</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>289151; 1047548</t>
+          <t>261743; 322870</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100513</t>
+          <t>108529</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>161801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>235865</t>
+          <t>270329</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86108; 125821</t>
+          <t>86855; 125901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82272; 122337</t>
+          <t>90956; 131596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127794; 172580</t>
+          <t>128631; 174992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72780; 182692</t>
+          <t>141129; 185179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>227072; 289482</t>
+          <t>225783; 286044</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>149855; 286486</t>
+          <t>241252; 300679</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>193491</t>
+          <t>196607</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>241085</t>
+          <t>256644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>434576</t>
+          <t>453251</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109181; 152906</t>
+          <t>111679; 156566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169098; 219655</t>
+          <t>172507; 224723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>164221; 213691</t>
+          <t>164366; 214922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194168; 269353</t>
+          <t>233942; 283135</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>288856; 356066</t>
+          <t>289972; 357745</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>385470; 472788</t>
+          <t>421921; 489385</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>450601; 532950</t>
+          <t>447787; 530340</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535648; 1357470</t>
+          <t>492282; 581716</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>623660; 717621</t>
+          <t>621069; 719257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>519238; 689500</t>
+          <t>660448; 745858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1094059; 1227221</t>
+          <t>1093456; 1223456</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1146383; 2120306</t>
+          <t>1170974; 1290464</t>
         </is>
       </c>
     </row>
